--- a/docs/oc-regiones/pasajes-aereos-nacionales/region-del-maule.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/region-del-maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4885-100-CM26</t>
+          <t>1391-376-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>716.61</v>
+        <v>126.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4885-101-CM26</t>
+          <t>1978-245-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.976.200-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>653.02</v>
+        <v>338.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1596-221-CM26</t>
+          <t>732-169-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>214.75</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1596-223-CM26</t>
+          <t>732-184-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,2568 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>154.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>732-187-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>206.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>732-197-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>203.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>732-196-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>99.42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>732-201-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>337.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>732-207-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>199.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1596-94-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>439.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>732-215-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>283.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>732-213-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>290.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2318-365-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>2329.94</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>732-224-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>615.96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>732-226-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>307.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2318-366-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>514.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>732-230-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>186.76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>732-231-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>841.79</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>732-240-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.701.000-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>216.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2177-51-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>316.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1208102-21-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>309.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1208102-24-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>183.78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1872-6-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>102.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1596-164-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>104.16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2177-66-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>256.96</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1230851-30-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>227.66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1230851-29-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>464.31</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1230851-32-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>65.061.839-4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE CULTURA DE TALCA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>143.72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3206-228-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.264.500-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1397.95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1596-189-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>252.53</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2318-712-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>594.88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4885-70-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1704.37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4885-69-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>179.95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1391-1611-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.004.051-9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>253.91</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1596-231-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>779.88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2177-82-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>316.89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1208102-54-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>160.36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4885-139-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>711.89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4885-140-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>235.91</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1872-14-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>437.36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4885-192-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1792.81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4885-195-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>452.96</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4885-100-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>716.61</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4885-101-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.976.200-2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>653.02</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1596-221-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>214.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1596-223-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>65.44</v>
       </c>
     </row>
